--- a/site/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,32 +605,164 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>h_01KTBHY6CPRYEDC5HG342E82EQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBHY6CPRYEDC5HG342E82EQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Access Policy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KTBHZ0F61WA9YHPDXZQZ4TKB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBHZ0F61WA9YHPDXZQZ4TKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Organizational Unit Policy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KTBJ8WNSMWWRZ3BDTNZWYA3S</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBJ8WNSMWWRZ3BDTNZWYA3S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Required Organizational Units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KTBJC1194NXHKDE41JK42PVQ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBJC1194NXHKDE41JK42PVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Forbidden Organizational Units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KTBJC49Z2YGBJF9RXW2K0H7G</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBJC49Z2YGBJF9RXW2K0H7G</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Attribute Policy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Watchdog Insights</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
         </is>

--- a/site/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,64 +705,152 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attribute Policy</t>
+          <t>Group Policy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+          <t>h_01KTC1YYZA43BETFXVRV4D00R9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTC1YYZA43BETFXVRV4D00R9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Required Groups</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>h_01KTC1YYZB4SX49NJGZ8WWAPM3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTC1YYZB4SX49NJGZ8WWAPM3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Forbidden Groups</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KTC1YYZBDABRKNE34MJ6PQ8J</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTC1YYZBDABRKNE34MJ6PQ8J</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Directory Policy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KTC1YYZB438W48Y7PE48WTY0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTC1YYZB438W48Y7PE48WTY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Attribute Policy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KTBHZ41GYMA7WJW3HWQN1P7S</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ7DS5DDR5Y7K4VM0Z4F7SJ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Watchdog Insights</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-Dayforce-to-Active-Directory-Integration/#h_01KQ9AKSTAGRHHECR0BZP7CA26</t>
         </is>
